--- a/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
@@ -596,13 +596,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A blog turns a title into a URL slug by lower-casing it and replacing spaces with hyphens. Read a title and print its slug.
+          <t>Priya writes for her college fest's blog. Every post needs a web address, and the website builds it from the post's title: all letters made small, and every space replaced with a hyphen. This hyphen-joined, lower-case form is called a "slug" — the friendly text you see at the end of a web link.
+Write a program that reads a title on one line, converts it to lower case, replaces each space with a hyphen (`-`), and prints the resulting slug.
 ### Input Format
-- Line 1: A title
+- Line 1: A title (words separated by spaces)
 ### Output Format
 ```
 hello-world
 ```
+### Example Walkthrough
+The sample input is `Hello World`. Making all letters small gives `hello world`, and replacing the space with a hyphen gives `hello-world`, which is exactly what the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -740,13 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read a word and print its first and last characters separated by a space. A one-letter word uses the same character for both.
+          <t>At Arjun's coaching class, the teacher plays a quick vocabulary game: she calls out a word, and students must shout back its first and last letters. Arjun wants a small program that gives the correct answer instantly.
+Read one word and print its first character and its last character, separated by a single space. If the word has only one letter, that same letter is both the first and the last, so print it twice.
 ### Input Format
 - Line 1: A word
 ### Output Format
 ```
 p n
 ```
+### Example Walkthrough
+The sample word is `python`. Its first character is `p` and its last character is `n`, so the program prints `p n` with one space between them.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -884,13 +890,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A field removes accidental spaces at the start and end of input. Read a line, strip the surrounding spaces, and print the result inside square brackets, like [text].
+          <t>Students filling the online hostel registration form often press the spacebar by mistake before or after typing their name. The college office software must clean up these stray spaces before saving each entry, without disturbing the text in the middle.
+Read one line of text, remove any spaces at the start and end (spaces between words stay as they are), and print the cleaned text inside square brackets, like `[text]`, so the trimmed edges are easy to see.
 ### Input Format
-- Line 1: A line of text with possible surrounding spaces
+- Line 1: A line of text that may have extra spaces at the start and end
 ### Output Format
 ```
 [hello]
 ```
+### Example Walkthrough
+The sample input is `  hello  ` — the word `hello` with two spaces on each side. Stripping the spaces from both ends leaves just `hello`, and wrapping it in square brackets prints `[hello]`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1029,13 +1038,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A badge printer shows a person's initials. Read a full name and print the capitalised first letter of each word joined together.
+          <t>The college library prints ID badges for its student volunteers, but long names never fit on the small card. So the badge machine prints only the person's initials — the first letter of each part of the name, in capitals.
+Read a full name (words separated by spaces), take the first letter of each word, convert those letters to capitals, and print them joined together with nothing in between.
 ### Input Format
-- Line 1: A full name
+- Line 1: A full name (words separated by spaces)
 ### Output Format
 ```
 JRT
 ```
+### Example Walkthrough
+The sample name `john ronald tolkien` has three words. Their first letters are `j`, `r` and `t`; capitalised and joined together they become `JRT`, which is what the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1176,13 +1188,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Read a word and print 'Yes' if it reads the same forwards and backwards (ignoring case), otherwise print 'No'.
+          <t>On the long bus ride back to the hostel, Kavya and her friends play a word game: spot words that read the same forwards and backwards, like `madam`. Such a word is called a palindrome, and Kavya wants a program to settle their arguments.
+Read one word and print `Yes` if it reads the same forwards and backwards, treating capital and small letters as equal; otherwise print `No`.
 ### Input Format
 - Line 1: A word
 ### Output Format
 ```
 Yes
 ```
+### Example Walkthrough
+The sample word is `racecar`. Written backwards it is still `racecar`, so it is a palindrome and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1321,7 +1336,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A chat filter replaces a banned word with '***'. Read a line of text, then the banned word, and print the line with every occurrence replaced.
+          <t>The coding club's group chat has a small moderation bot. Whenever someone types a word from the banned list, the bot must hide it by replacing it with `***` before the message appears on screen.
+Read a line of text, then read the banned word on the next line. Replace every occurrence of the banned word in the text with `***` and print the resulting line.
 ### Input Format
 - Line 1: A line of text
 - Line 2: The banned word
@@ -1329,6 +1345,8 @@
 ```
 this is ***
 ```
+### Example Walkthrough
+The sample text is `this is bad` and the banned word is `bad`. The word appears once, at the end, so it is replaced with `***` and the program prints `this is ***`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1474,15 +1492,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A till prints a receipt line. Read an item name, a quantity, and a unit price, then print a line like 'Coffee x 3 = 7.50' with the total shown to exactly 2 decimal places.
+          <t>The canteen near the exam hall has installed a new billing machine. For every item sold, the machine prints one receipt line showing the item's name, how many were bought, and the total amount for that item.
+Read an item name, then a quantity (a whole number), then a unit price. Multiply the quantity by the unit price and print a line in the exact form `name x quantity = total`, with the total shown to exactly 2 decimal places.
 ### Input Format
 - Line 1: Item name
-- Line 2: Quantity
+- Line 2: Quantity (a whole number)
 - Line 3: Unit price
 ### Output Format
 ```
 Coffee x 3 = 7.50
 ```
+### Example Walkthrough
+The sample input is `Coffee`, quantity 3 and unit price 2.5. Multiplying 3 by 2.5 gives 7.5, which written with two decimal places is `7.50`, so the program prints `Coffee x 3 = 7.50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1636,13 +1657,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A payment page hides all but the last 4 digits of a card number, showing an asterisk for each hidden digit. Read the number and print the masked version.
+          <t>Rohit is paying his semester exam fee online. On the payment page, his saved card number is never shown in full — for safety, every digit except the last four is hidden behind an asterisk (`*`).
+Read a card number (digits only) and print the masked version: one `*` for each digit except the last four, followed by the last four digits exactly as they are.
 ### Input Format
 - Line 1: A card number (digits only)
 ### Output Format
 ```
 ************5678
 ```
+### Example Walkthrough
+The sample number `1234567812345678` has 16 digits. The first 12 digits are each replaced by `*`, and the last four digits `5678` are kept, so the program prints `************5678`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1780,14 +1804,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Encrypt a message by shifting each lower-case letter forward by K places in the alphabet, wrapping from z back to a. Non-letters stay unchanged. Read the message and K, then print the encrypted text.
+          <t>Dev and Sam, two hostel roommates, pass secret notes using an old trick called the Caesar cipher: every letter in the message is shifted forward in the alphabet by a fixed number of places, wrapping around from `z` back to `a`.
+Read a lower-case message, then a number `K`. Shift each letter forward by `K` places in the alphabet (wrapping from `z` back to `a`); anything that is not a letter, like a space or a digit, stays unchanged. Print the encrypted message.
 ### Input Format
 - Line 1: The message (lower-case)
-- Line 2: K, the shift
+- Line 2: K, the number of places to shift
 ### Output Format
 ```
 bcd
 ```
+### Example Walkthrough
+The sample message is `abc` with `K = 1`. Shifting each letter forward one place turns `a` into `b`, `b` into `c`, and `c` into `d`, so the program prints `bcd`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1939,7 +1966,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Read two lines of text and print 'Yes' if they are anagrams of each other (same letters in any order), ignoring case and spaces; otherwise print 'No'.
+          <t>Ananya loves the word puzzle in the Sunday newspaper: it gives two words and asks whether one is just the other with its letters rearranged — for example `heart` and `earth`. Such a pair is called an anagram, and she wants a program to check her answers.
+Read two lines of text and print `Yes` if they are anagrams of each other — made of exactly the same letters in any order — treating capital and small letters as equal and ignoring spaces. Otherwise print `No`.
 ### Input Format
 - Line 1: First text
 - Line 2: Second text
@@ -1947,6 +1975,8 @@
 ```
 Yes
 ```
+### Example Walkthrough
+The sample inputs are `listen` and `silent`. Both words use the letters `e`, `i`, `l`, `n`, `s` and `t` exactly once each, so they are anagrams and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,12 +624,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -768,12 +781,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -783,7 +806,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>indexing-slicing</t>
+          <t>indexing-and-slicing</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -915,12 +938,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,7 +1027,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
@@ -1005,7 +1038,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>     </t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1063,12 +1096,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,7 +1121,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>indexing-slicing</t>
+          <t>split-and-join</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1213,12 +1256,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1228,7 +1281,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>indexing-slicing</t>
+          <t>indexing-and-slicing</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1292,7 +1345,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
@@ -1362,12 +1415,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1519,12 +1582,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,7 +1607,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>formatting</t>
+          <t>string-formatting</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1682,12 +1755,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1697,7 +1780,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>indexing-slicing</t>
+          <t>indexing-and-slicing</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1799,10 +1882,504 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - First Three Characters</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for First Three Characters. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+Pyt
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>indexing-and-slicing</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Pyt</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>abcdef</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>coding</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>cod</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ByteXL</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Byt</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>s=input()
+print(s[:3])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Ends With Dot</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Ends With Dot. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+Yes
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Hello.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>No dot</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>end.</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Python!</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>s=input()
+print("Yes" if s.endswith(".") else "No")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Caesar Cipher</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Dev and Sam, two hostel roommates, pass secret notes using an old trick called the Caesar cipher: every letter in the message is shifted forward in the alphabet by a fixed number of places, wrapping around from `z` back to `a`.
 Read a lower-case message, then a number `K`. Shift each letter forward by `K` places in the alphabet (wrapping from `z` back to `a`); anything that is not a letter, like a space or a digit, stays unchanged. Print the encrypted message.
@@ -1820,131 +2397,141 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>indexing-slicing</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string-methods</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>abc
 1</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>bcd</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>xyz
 3</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>hello
 5</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>mjqqt</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>a
 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>hello world
 1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>ifmmp xpsme</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>abc xyz
 26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>abc xyz</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>z
 25</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>text = input()
 k = int(input())
@@ -1958,13 +2545,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Anagram Check</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Ananya loves the word puzzle in the Sunday newspaper: it gives two words and asks whether one is just the other with its letters rearranged — for example `heart` and `earth`. Such a pair is called an anagram, and she wants a program to check her answers.
 Read two lines of text and print `Yes` if they are anagrams of each other — made of exactly the same letters in any order — treating capital and small letters as equal and ignoring spaces. Otherwise print `No`.
@@ -1982,131 +2569,141 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>listen
 silent</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>hello
 world</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Dormitory
 Dirty Room</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>abc
 cba</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>aabbcc
 abcabc</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>The Morse Code
 Here Come Dots</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>a = input().lower().replace(" ", "")
 b = input().lower().replace(" ", "")
@@ -2114,13 +2711,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Shout It Out</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A chat app has a 'caps' button. Read one line of text and print it entirely in upper case.
 ### Input Format
@@ -2129,142 +2726,154 @@
 ```
 HELLO WORLD
 ```
+### Example Walkthrough
+In the sample, the input is `hello world`. Converting every letter to upper case gives `HELLO WORLD`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>HELLO WORLD</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>PYTHON</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>ALREADY UPPER</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>ALREADY UPPER</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>MiXeD CaSe 123</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>MIXED CASE 123</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>the quick brown fox jumps</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>THE QUICK BROWN FOX JUMPS</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>text = input()
 print(text.upper())</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Message Length</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A text box shows a character counter. Read one line and print how many characters it contains.
 ### Input Format
@@ -2273,143 +2882,155 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the input is `Hello`. It has `5` characters, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>string-basics</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>   </t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>supercalifragilisticexpialidocious</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>text = input()
 print(len(text))</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Preview Snippet</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>A search result shows only the first 3 characters of a title as a preview. Read a title and print its first 3 characters (or the whole title if it is shorter).
 ### Input Format
@@ -2418,142 +3039,154 @@
 ```
 int
 ```
+### Example Walkthrough
+In the sample, the title is `international`. Its first three characters are `int`, so the program prints `int`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>indexing-slicing</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>indexing-and-slicing</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>introduction</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>hi</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>hi</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>byte</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>byt</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>This Is A Long Title</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Thi</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>title = input()
 print(title[:3])</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Word Count</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A writing tool counts words. Read a line of text and print how many words it contains (words are separated by spaces).
 ### Input Format
@@ -2562,143 +3195,155 @@
 ```
 4
 ```
+### Example Walkthrough
+In the sample, the input is `the quick brown fox`. It splits into `4` words, so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>the quick brown fox</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>a b c d</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>   </t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>a  b   c    d     e</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>text = input()
 print(len(text.split()))</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Proper Name</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>A form tidies a name so each word starts with a capital letter. Read a name and print it in title case.
 ### Input Format
@@ -2707,142 +3352,154 @@
 ```
 John Doe
 ```
+### Example Walkthrough
+In the sample, the input is `john doe`. Converting it to title case gives `John Doe`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>john doe</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>John Doe</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>mary jane watson</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Mary Jane Watson</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>alice</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>MARY JANE</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Mary Jane</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>mcdonald o'brien</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Mcdonald O'Brien</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>anne marie de la cruz</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Anne Marie De La Cruz</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>name = input()
 print(name.title())</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Echo Chamber</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>A sound effect repeats a short sound N times. Read the text, then N, and print the text repeated N times with no spaces between copies.
 ### Input Format
@@ -2852,131 +3509,143 @@
 ```
 ababab
 ```
+### Example Walkthrough
+In the sample, the text is `ab` and `N` is `3`. Repeating `ab` three times with no separator gives `ababab`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>string-basics</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>ab
 3</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>ababab</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>x
 5</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>xxxxx</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>hi
 1</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>hi</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>a
 0</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>hello
 2</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>hellohello</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>z
 10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>zzzzzzzzzz</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>ab
 100</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>abababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababab</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>text = input()
 n = int(input())
@@ -2984,13 +3653,505 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Clean Username</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Clean Username. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Username
+### Output Format
+```
+asha
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>string-methods</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Asha  </t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>asha</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ROHAN</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>rohan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Meena</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>meena</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabir </t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>kabir</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Z oya</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>z oya</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DEV PATEL </t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>dev patel</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>print(input().strip().lower())</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Join Words</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Join Words. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Words
+### Output Format
+```
+hello-world
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>hello world</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>hello-world</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>python foundations</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>python-foundations</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>a b c</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>a-b-c</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Byte XL Course</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Byte-XL-Course</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>data types</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>data-types</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>clean code now</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>clean-code-now</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>print("-".join(input().split()))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Word Reverser</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read a sentence and print its words in reverse order, separated by single spaces.
 ### Input Format
@@ -2999,142 +4160,154 @@
 ```
 world hello
 ```
+### Example Walkthrough
+In the sample, the input is `hello world`. Reversing the order of its words gives `world hello`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>world hello</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>one two three</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>three two one</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>b a</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>the quick brown fox jumps over</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>over jumps fox brown quick the</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t xml:space="preserve">  extra   spaces   here  </t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>here spaces extra</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>words = input().split()
 print(" ".join(words[::-1]))</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Swap Case</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A novelty keyboard swaps the case of every letter. Read a line and print it with upper-case letters made lower-case and vice versa.
 ### Input Format
@@ -3143,138 +4316,150 @@
 ```
 hELLO wORLD
 ```
+### Example Walkthrough
+In the sample, the input is `Hello World`. Swapping each letter's case gives `hELLO wORLD`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Hello World</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>hELLO wORLD</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>PyThOn</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>pYtHoN</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>abcXYZ</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>ABCxyz</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>ALLCAPS</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>allcaps</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1234 mixed CASE 5678</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1234 MIXED case 5678</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>text = input()
 print(text.swapcase())</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Find the Word</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a line of text, then a word to search for. Print the index where the word first appears, or -1 if it does not appear.
 ### Input Format
@@ -3284,136 +4469,148 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the text is `hello world` and the word to find is `world`. It first appears at index `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>hello world
 world</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>abcabc
 bc</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>python
 xyz</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t xml:space="preserve">hello
 </t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>aaaa
 aa</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>the quick brown fox
 brown</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>text = input()
 word = input()
@@ -3421,13 +4618,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Count Substring</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line of text, then a smaller piece of text. Print how many times the piece appears in the line (non-overlapping).
 ### Input Format
@@ -3437,136 +4634,148 @@
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the text is `ababab` and the piece is `ab`. It appears `3` times without overlapping, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>banana
 a</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>aaaa
 aa</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>hello
 z</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>mississippi
 ss</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>aaaaaa
 aaa</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t xml:space="preserve">hello world
  </t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>text = input()
 piece = input()
@@ -3574,13 +4783,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Email Domain</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read an email address and print just the domain part that comes after the '@' sign.
 ### Input Format
@@ -3589,142 +4798,154 @@
 ```
 example.com
 ```
+### Example Walkthrough
+In the sample, the email is `user@example.com`. Splitting on `@` and keeping the second part gives `example.com`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>john@example.com</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>example.com</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>a.b@mail.co.in</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>mail.co.in</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>user@site.org</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>site.org</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>x@y.co</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>y.co</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>first.last@sub.domain.com</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>sub.domain.com</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>a1@test123.net</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>test123.net</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>name@company.io</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>company.io</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>email = input()
 print(email.split("@")[1])</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Starts With</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of text, then a prefix. Print 'Yes' if the text starts with that prefix, otherwise print 'No'.
 ### Input Format
@@ -3734,136 +4955,148 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the text is `hello world` and the prefix is `hello`. Since the text starts with that prefix, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>python
 py</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>hello
 hi</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>coding
 cod</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t xml:space="preserve">hello
 </t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>abc
 abcd</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>the quick fox
 the quick</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>text = input()
 prefix = input()
@@ -3871,13 +5104,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Vowels and Consonants</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a line of text and print two numbers: how many vowels and how many consonants it contains, separated by a space. Count letters only and ignore case.
 ### Input Format
@@ -3886,129 +5119,141 @@
 ```
 5 4
 ```
+### Example Walkthrough
+In the sample, the input is `education`. It has `5` vowels (`e`, `u`, `a`, `i`, `o`) and `4` consonants (`d`, `c`, `t`, `n`), so the program prints `5 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>5 4</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0 3</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>AEIOU bcd</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>5 3</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>1 0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>bcdfg</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0 5</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>The Quick Brown Fox</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>5 11</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>aaaaaeeeee</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>10 0</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>text = input().lower()
 vowels = consonants = 0
@@ -4022,13 +5267,659 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Middle Slice</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Middle Slice. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+ytho
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>indexing-and-slicing</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ytho</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>estin</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ByteXL</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>yteX</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>s=input()
+print(s[1:-1])</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Count Word</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Count Word. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Sentence
+- Line 2: Word
+### Output Format
+```
+2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>cat dog cat
+cat</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>one two one
+one</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>hello
+hello</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>a a a
+a</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>red blue red
+blue</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Python python
+Python</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>x y z
+a</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>s=input(); w=input(); print(s.split().count(w))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Mask Email Name</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Mask Email Name. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Email
+### Output Format
+```
+****@mail.com
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>string-methods</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>asha@mail.com</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>****@mail.com</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>r@x.in</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>*@x.in</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>meena@college.edu</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>*****@college.edu</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dev.patel@test.org</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>*********@test.org</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>a@b.c</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>*@b.c</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>longname@site.com</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>********@site.com</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>zoya@byte.in</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>****@byte.in</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>e=input(); name,domain=e.split("@"); print("*"*len(name)+"@"+domain)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Most Frequent Character</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read a line of text and print the character that appears most often. If several characters tie, print the one that appears earliest in the text.
 ### Input Format
@@ -4037,129 +5928,141 @@
 ```
 i
 ```
+### Example Walkthrough
+In the sample, the input is `mississippi`. The letters `i` and `s` both appear `4` times, but `i` appears earlier in the text, so the program prints `i`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>aabbbcc</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>abcabc</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>zzzzzzz</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>abcdefgghh</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>text = input()
 best = ""
@@ -4173,13 +6076,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Word Frequency</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a sentence and, for each distinct word in order of first appearance, print the word and how many times it appears, separated by a space, one per line.
 ### Input Format
@@ -4190,137 +6093,149 @@
 b 2
 c 1
 ```
+### Example Walkthrough
+In the sample, the input is `a b a c a b`. In order of first appearance, `a` appears `3` times, `b` appears `2` times, and `c` appears `1` time, so the program prints `a 3`, `b 2`, and `c 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>a b a c b a</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>a 3
 b 2
 c 1</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>hello hello</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>hello 2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>one two two three three three</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>one 1
 two 2
 three 3</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>a 1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>x 1
 y 1
 z 1</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>same same same same</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>same 4</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>a b c a b c a b c a</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>a 4
 b 3
 c 3</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>words = input().split()
 seen = []
@@ -4332,13 +6247,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Make an Acronym</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a phrase and print its acronym: the capitalised first letter of each word, joined together.
 ### Input Format
@@ -4347,129 +6262,141 @@
 ```
 RAM
 ```
+### Example Walkthrough
+In the sample, the phrase is `random access memory`. Taking the capitalised first letter of each word gives `R`, `A`, and `M`, joined into `RAM`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>random access memory</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>RAM</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>portable document format</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>as soon as possible</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>ASAP</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>already Capitalized Words</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>ACW</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>a b c d e f g h</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>ABCDEFGH</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>words = input().split()
 acronym = ""
@@ -4479,13 +6406,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Remove Duplicate Characters</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a word and print it with duplicate characters removed, keeping only the first occurrence of each character in order.
 ### Input Format
@@ -4494,129 +6421,141 @@
 ```
 progamin
 ```
+### Example Walkthrough
+In the sample, the word is `programming`. Keeping only the first occurrence of each character in order gives `progamin`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>indexing-slicing</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>searching-and-membership</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>programming</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>progamin</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>aabbcc</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>abcabc</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>aaaaaaa</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>misp</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>word = input()
 result = ""
@@ -4627,13 +6566,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Run-Length Encoding</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Compress a word by replacing runs of the same character with the character followed by how many times it repeats. For example 'aaabbc' becomes 'a3b2c1'. Read a word and print its compressed form.
 ### Input Format
@@ -4642,129 +6581,141 @@
 ```
 a3b2c1
 ```
+### Example Walkthrough
+In the sample, the word is `aaabbc`. The runs are three `a`s, two `b`s, and one `c`, so the program prints `a3b2c1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>indexing-slicing</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>indexing-and-slicing</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>aaabbc</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>a3b2c1</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>a1b1c1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>wwwwww</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>w6</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>a1</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>aabbccddee</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>a2b2c2d2e2</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>z1</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>aaaaaaaaaabbbbbbbbbb</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>a10b10</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>word = input()
 result = ""
@@ -4780,13 +6731,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Longest Word</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a sentence and print its longest word. If several words tie for the longest, print the one that appears first.
 ### Input Format
@@ -4795,129 +6746,141 @@
 ```
 quick
 ```
+### Example Walkthrough
+In the sample, the input is `the quick brown fox`. `quick` and `brown` are tied for longest at `5` letters, but `quick` appears first, so the program prints `quick`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>string-methods</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>the quick brown fox</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>i love programming</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>programming</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>a bb ccc dd</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>ccc</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>same size word test</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>a bb aa cc</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>bb</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>supercalifragilistic is long but hi is not</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>supercalifragilistic</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>words = input().split()
 best = words[0]
@@ -4928,15 +6891,15 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Last Name First</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>A directory lists people as 'Last, First'. Read N, then N lines each with a first and last name separated by a space, and print each name reformatted as 'Last, First', one per line.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A directory lists people as 'Last, First'. Read `N`, then `N` lines each with a first and last name separated by a space, and print each name reformatted as 'Last, First', one per line.
 ### Input Format
 - Line 1: N
 - Next N lines: 'first last'
@@ -4945,83 +6908,95 @@
 doe, john
 jane, mary
 ```
+### Example Walkthrough
+In the sample, `N` is `2` with `john doe` and `mary jane`. Reformatting each gives `doe, john` and `jane, mary`, printed one per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>formatting</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>string-formatting</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>2
 john doe
 mary jane</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>doe, john
 jane, mary</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1
 alice smith</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>smith, alice</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>3
 a b
@@ -5029,30 +7004,30 @@
 e f</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>b, a
 d, c
 f, e</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1
 x y</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>y, x</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>4
 a b
@@ -5061,7 +7036,7 @@
 g h</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>b, a
 d, c
@@ -5069,25 +7044,497 @@
 h, g</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2
 john ronald
 mary jane</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>ronald, john
 jane, mary</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 for _ in range(n):
     first, last = input().split()
     print(f"{last}, {first}")</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Compress Runs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Compress Runs. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+a3b2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>text-processing</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>aaabb</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>a3b2</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>a1b1c1</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>zzzz</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>z4</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>aabcccccaaa</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>a2b1c5a3</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>111223</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>132231</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>s=input(); out=[]; prev=s[0]; c=1
+for ch in s[1:]:
+ if ch==prev: c+=1
+ else: out.append(prev+str(c)); prev=ch; c=1
+out.append(prev+str(c))
+print("".join(out))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Reverse Words</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Reverse Words. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+three two one
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>split-and-join</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>one two three</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>three two one</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>a b</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>b a</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Python is fun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>fun is Python</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>spaced words</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>words spaced</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>x y z q</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>q z y x</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ByteXL course</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>course ByteXL</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>print(" ".join(input().split()[::-1]))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Anagram Sorted</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Anagram Sorted. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First
+- Line 2: Second
+### Output Format
+```
+Yes
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>strings</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>text-processing</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>listen
+silent</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>abc
+abd</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>a
+a</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>triangle
+integral</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Dormitory
+dirtyroom</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>rat
+tar</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>hello
+world</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=input().lower().replace(" ",""); b=input().lower().replace(" ",""); print("Yes" if sorted(a)==sorted(b) else "No")</t>
         </is>
       </c>
     </row>

--- a/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
@@ -1887,16 +1887,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for First Three Characters. Read the input values and print the required result exactly.
+          <t>A ticketing system generates short boarding codes by taking the first three characters of a passenger's name.
+Read a line of text and print its first three characters, in order. If the text has fewer than three characters, print the text exactly as it is (there aren't enough characters to trim).
 ### Input Format
 - Line 1: Text
 ### Output Format
 ```
 Pyt
 ```
+### Example Walkthrough
+In the sample, the text is `Python`. Its first three characters are `P`, `y`, and `t`, so the program prints `Pyt`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The text may contain fewer than three characters, in which case the entire text is printed.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2041,16 +2044,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Ends With Dot. Read the input values and print the required result exactly.
+          <t>A sentence-checking tool in a writing app flags whether a line ends with proper punctuation.
+Read a line of text. If the last character of the text is a period (`.`), print `Yes`; otherwise print `No`.
 ### Input Format
 - Line 1: Text
 ### Output Format
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the text is `Hello.`. Its last character is `.`, so the program prints `Yes`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The check looks only at the very last character of the text.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3661,16 +3667,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Clean Username. Read the input values and print the required result exactly.
+          <t>A sign-up form on ByteXL's portal wants to store usernames in a clean, consistent form regardless of how a user typed them.
+Read a line containing a username. Remove any leading and trailing spaces, convert all letters to lower case, and print the result.
 ### Input Format
 - Line 1: Username
 ### Output Format
 ```
 asha
 ```
+### Example Walkthrough
+In the sample, the input is `  Asha  ` (with extra spaces around it). Removing the leading and trailing spaces gives `Asha`, and converting it to lower case gives `asha`, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Only leading and trailing spaces are removed; spaces between words, if any, are kept.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3814,16 +3823,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Join Words. Read the input values and print the required result exactly.
+          <t>A URL-building tool needs to turn a spoken phrase into a hyphen-separated slug fragment.
+Read a line of one or more words separated by spaces. Join the words together using a hyphen (`-`) between each pair, and print the result.
 ### Input Format
 - Line 1: Words
 ### Output Format
 ```
 hello-world
 ```
+### Example Walkthrough
+In the sample, the input is `hello world`, which splits into the words `hello` and `world`. Joining them with a hyphen gives `hello-world`, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Words may be separated by one or more spaces in the input, but the output uses exactly one hyphen between each pair of words.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5275,16 +5287,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Middle Slice. Read the input values and print the required result exactly.
+          <t>A word game removes the first and last letter of a word to create a new puzzle clue.
+Read a line of text. Print the text with its first and last character removed, keeping everything in between. If the text has two or fewer characters, nothing remains, so print an empty line.
 ### Input Format
 - Line 1: Text
 ### Output Format
 ```
 ytho
 ```
+### Example Walkthrough
+In the sample, the text is `Python`. Removing the first character `P` and the last character `n` leaves `ytho`, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- If the text has one or two characters, the result is empty and the program prints a blank line.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5359,7 +5374,6 @@
           <t>ab</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>abc</t>
@@ -5375,7 +5389,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
           <t>testing</t>
@@ -5421,7 +5434,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Count Word. Read the input values and print the required result exactly.
+          <t>A study app highlights how often a target word appears in a sentence to help students spot repetition.
+Read a sentence, then a word. Split the sentence into words wherever there is a space, and count how many of those words are exactly equal to the given word (matching is case-sensitive). Print the count.
 ### Input Format
 - Line 1: Sentence
 - Line 2: Word
@@ -5429,9 +5443,11 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the sentence is `cat dog cat` and the word is `cat`. Splitting the sentence gives the words `cat`, `dog`, `cat`, and exactly `2` of them equal `cat`, so the program prints `2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The match is case-sensitive and compares whole words only, not substrings.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5582,16 +5598,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Mask Email Name. Read the input values and print the required result exactly.
+          <t>A privacy feature in an email client hides the username part of an address before showing it on screen.
+Read an email address containing exactly one `@`. Replace every character before the `@` with an asterisk (`*`), keeping the same number of characters, then print the masked name followed by `@` and the domain part unchanged.
 ### Input Format
 - Line 1: Email
 ### Output Format
 ```
 ****@mail.com
 ```
+### Example Walkthrough
+In the sample, the email is `asha@mail.com`. The part before `@` is `asha`, which has 4 characters, so it becomes `****`. The domain `mail.com` after the `@` stays unchanged, so the program prints `****@mail.com`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The email contains exactly one `@` symbol separating the name from the domain.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7074,16 +7093,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Compress Runs. Read the input values and print the required result exactly.
+          <t>A simple file-compression demo shrinks text by replacing repeated runs of the same character with the character and its count.
+Read a line of text. Scan through it and group consecutive occurrences of the same character into runs. For each run, print the character followed by how many times it repeats, one run after another with no separators.
 ### Input Format
 - Line 1: Text
 ### Output Format
 ```
 a3b2
 ```
+### Example Walkthrough
+In the sample, the text is `aaabb`. It has a run of three `a`s followed by a run of two `b`s, so the program prints `a3b2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Every character in the input, including digits, is treated the same way when grouping runs.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7232,16 +7254,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Reverse Words. Read the input values and print the required result exactly.
+          <t>A puzzle app reverses the order of words in a sentence while keeping each word itself unchanged.
+Read a line of text. Split it into words wherever there is a space, reverse the order of the words, and print them back joined by single spaces.
 ### Input Format
 - Line 1: Text
 ### Output Format
 ```
 three two one
 ```
+### Example Walkthrough
+In the sample, the input is `one two three`, which splits into the words `one`, `two`, `three`. Reversing their order gives `three`, `two`, `one`, so the program prints `three two one`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Only the order of the words is reversed; the letters within each word stay the same.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7385,7 +7410,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Anagram Sorted. Read the input values and print the required result exactly.
+          <t>A word-puzzle app checks whether two phrases are anagrams of each other, ignoring case and spaces.
+Read two lines of text. Convert both to lower case and remove all spaces from each. If the sorted letters of the first line match the sorted letters of the second line exactly, print `Yes`; otherwise print `No`.
 ### Input Format
 - Line 1: First
 - Line 2: Second
@@ -7393,9 +7419,11 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the first line is `listen` and the second is `silent`. Neither has spaces, and after converting to lower case and sorting their letters, both become `eilnst`, so the program prints `Yes`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Comparison ignores letter case and spaces but considers every other character, including punctuation and digits.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
@@ -1887,18 +1887,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A ticketing system generates short boarding codes by taking the first three characters of a passenger's name.
-Read a line of text and print its first three characters, in order. If the text has fewer than three characters, print the text exactly as it is (there aren't enough characters to trim).
+          <t>An airline's booking system generates a short destination code for every ticket by taking just the first three letters of the city name typed in by the check-in agent.
+Write a program that reads a city name and prints only its first three characters. If the name has fewer than three characters, print the whole name.
 ### Input Format
-- Line 1: Text
+- Line 1: City name
 ### Output Format
 ```
 Pyt
 ```
 ### Example Walkthrough
-In the sample, the text is `Python`. Its first three characters are `P`, `y`, and `t`, so the program prints `Pyt`.
+In the sample, the city name is `Python`. Taking the first three characters gives `Pyt`, which the program prints.
 ### Constraints
-- The text may contain fewer than three characters, in which case the entire text is printed.
+- The input is a valid line of text with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -2044,18 +2044,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A sentence-checking tool in a writing app flags whether a line ends with proper punctuation.
-Read a line of text. If the last character of the text is a period (`.`), print `Yes`; otherwise print `No`.
+          <t>A grammar checker flags whether a sentence a student submits ends with proper punctuation, specifically a full stop.
+Write a program that reads a line of text and prints `Yes` if it ends with a period (`.`), and `No` otherwise.
 ### Input Format
-- Line 1: Text
+- Line 1: A sentence
 ### Output Format
 ```
 Yes
 ```
 ### Example Walkthrough
-In the sample, the text is `Hello.`. Its last character is `.`, so the program prints `Yes`.
+In the sample, the text is `Hello.`. Since the last character is a period, the program prints `Yes`. The text `Hello` (no period) would print `No`.
 ### Constraints
-- The check looks only at the very last character of the text.
+- The input is a valid line of text with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3667,8 +3667,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A sign-up form on ByteXL's portal wants to store usernames in a clean, consistent form regardless of how a user typed them.
-Read a line containing a username. Remove any leading and trailing spaces, convert all letters to lower case, and print the result.
+          <t>A signup form normalizes every username before storing it in the database, so `  Asha  ` and `asha` are treated as the same account: stray spaces at the ends are trimmed and every letter is converted to lower case.
+Write a program that reads a username, removes any leading or trailing spaces, converts it to lower case, and prints the result.
 ### Input Format
 - Line 1: Username
 ### Output Format
@@ -3676,9 +3676,9 @@
 asha
 ```
 ### Example Walkthrough
-In the sample, the input is `  Asha  ` (with extra spaces around it). Removing the leading and trailing spaces gives `Asha`, and converting it to lower case gives `asha`, which the program prints.
+In the sample, the input is `  Asha  `. Trimming the spaces gives `Asha`, and converting to lower case gives `asha`, which the program prints.
 ### Constraints
-- Only leading and trailing spaces are removed; spaces between words, if any, are kept.
+- The input is a valid line of text.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3823,18 +3823,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A URL-building tool needs to turn a spoken phrase into a hyphen-separated slug fragment.
-Read a line of one or more words separated by spaces. Join the words together using a hyphen (`-`) between each pair, and print the result.
+          <t>A photo-sharing app turns a caption typed with spaces into a single hashtag by joining the words together with hyphens instead of spaces.
+Write a program that reads a line of words separated by spaces and prints them joined together with a single hyphen (`-`) between each pair of words.
 ### Input Format
-- Line 1: Words
+- Line 1: Words separated by spaces
 ### Output Format
 ```
 hello-world
 ```
 ### Example Walkthrough
-In the sample, the input is `hello world`, which splits into the words `hello` and `world`. Joining them with a hyphen gives `hello-world`, which the program prints.
+In the sample, the input is `hello world`. Splitting it gives the words `hello` and `world`, and joining them with a hyphen gives `hello-world`, which the program prints.
 ### Constraints
-- Words may be separated by one or more spaces in the input, but the output uses exactly one hyphen between each pair of words.
+- The input is a valid line of text with at least one word.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5287,18 +5287,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A word game removes the first and last letter of a word to create a new puzzle clue.
-Read a line of text. Print the text with its first and last character removed, keeping everything in between. If the text has two or fewer characters, nothing remains, so print an empty line.
+          <t>A text editor's "trim edges" feature strips away the very first and last character of any word a user selects, leaving just the middle portion behind.
+Write a program that reads a word and prints it with its first and last characters removed. If the word has one or two characters, print an empty line.
 ### Input Format
-- Line 1: Text
+- Line 1: A word
 ### Output Format
 ```
 ytho
 ```
 ### Example Walkthrough
-In the sample, the text is `Python`. Removing the first character `P` and the last character `n` leaves `ytho`, which the program prints.
+In the sample, the word is `Python`. Removing the first character (`P`) and the last character (`n`) leaves `ytho`, which the program prints.
 ### Constraints
-- If the text has one or two characters, the result is empty and the program prints a blank line.
+- The input is a valid word with no spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5434,19 +5434,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A study app highlights how often a target word appears in a sentence to help students spot repetition.
-Read a sentence, then a word. Split the sentence into words wherever there is a space, and count how many of those words are exactly equal to the given word (matching is case-sensitive). Print the count.
+          <t>An analytics tool checks how many times a specific keyword appears among the words of a sentence a user has typed, to measure keyword repetition. The match must be an exact, case-sensitive whole word, not a substring.
+Write a program that reads a sentence on one line and a target word on the next line, then prints how many of the sentence's space-separated words exactly match the target word.
 ### Input Format
-- Line 1: Sentence
-- Line 2: Word
+- Line 1: A sentence (words separated by spaces)
+- Line 2: The target word
 ### Output Format
 ```
 2
 ```
 ### Example Walkthrough
-In the sample, the sentence is `cat dog cat` and the word is `cat`. Splitting the sentence gives the words `cat`, `dog`, `cat`, and exactly `2` of them equal `cat`, so the program prints `2`.
+In the sample, the sentence is `cat dog cat` and the target word is `cat`. Splitting the sentence into words gives `cat`, `dog`, and `cat`, of which two exactly match `cat`, so the program prints `2`.
 ### Constraints
-- The match is case-sensitive and compares whole words only, not substrings.
+- The inputs are valid lines of text with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5598,18 +5598,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A privacy feature in an email client hides the username part of an address before showing it on screen.
-Read an email address containing exactly one `@`. Replace every character before the `@` with an asterisk (`*`), keeping the same number of characters, then print the masked name followed by `@` and the domain part unchanged.
+          <t>A public leaderboard shows partial email addresses for privacy: the part before the `@` is replaced with the same number of asterisks, while the domain after the `@` stays visible.
+Write a program that reads an email address and prints it with the part before the `@` replaced by that many asterisks, keeping the `@` and everything after it unchanged.
 ### Input Format
-- Line 1: Email
+- Line 1: An email address in the form `name@domain`
 ### Output Format
 ```
 ****@mail.com
 ```
 ### Example Walkthrough
-In the sample, the email is `asha@mail.com`. The part before `@` is `asha`, which has 4 characters, so it becomes `****`. The domain `mail.com` after the `@` stays unchanged, so the program prints `****@mail.com`.
+In the sample, the email is `asha@mail.com`. The part before `@` is `asha`, which has 4 characters, so it becomes `****`, and the program prints `****@mail.com`.
 ### Constraints
-- The email contains exactly one `@` symbol separating the name from the domain.
+- The input is a valid email address containing exactly one `@`.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7093,18 +7093,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A simple file-compression demo shrinks text by replacing repeated runs of the same character with the character and its count.
-Read a line of text. Scan through it and group consecutive occurrences of the same character into runs. For each run, print the character followed by how many times it repeats, one run after another with no separators.
+          <t>A simple image tool draws pixel rows as sequences of colored strokes, and compresses each row for storage by writing each repeated color once followed by how many pixels in a row had that color.
+Write a program that reads a string and prints its run-length encoding: each maximal run of the same consecutive character replaced by that character followed by the count of how many times it repeats, with no separators between runs.
 ### Input Format
-- Line 1: Text
+- Line 1: A string with no spaces
 ### Output Format
 ```
 a3b2
 ```
 ### Example Walkthrough
-In the sample, the text is `aaabb`. It has a run of three `a`s followed by a run of two `b`s, so the program prints `a3b2`.
+In the sample, the string is `aaabb`. The first run is `a` repeated 3 times (`a3`), followed by `b` repeated 2 times (`b2`), so the program prints `a3b2`.
 ### Constraints
-- Every character in the input, including digits, is treated the same way when grouping runs.
+- The input is a valid non-empty string with no spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7254,18 +7254,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A puzzle app reverses the order of words in a sentence while keeping each word itself unchanged.
-Read a line of text. Split it into words wherever there is a space, reverse the order of the words, and print them back joined by single spaces.
+          <t>A teleprompter app has a "word-order drill" mode for practicing sentences backwards: it takes a sentence and reads the words out in reverse order, without spelling any individual word backwards.
+Write a program that reads a sentence and prints its words in reverse order, separated by single spaces.
 ### Input Format
-- Line 1: Text
+- Line 1: A sentence (words separated by spaces)
 ### Output Format
 ```
 three two one
 ```
 ### Example Walkthrough
-In the sample, the input is `one two three`, which splits into the words `one`, `two`, `three`. Reversing their order gives `three`, `two`, `one`, so the program prints `three two one`.
+In the sample, the sentence is `one two three`. Splitting it into words gives `one`, `two`, `three`, and reversing their order gives `three`, `two`, `one`, so the program prints `three two one`.
 ### Constraints
-- Only the order of the words is reversed; the letters within each word stay the same.
+- The input is a valid line of text with at least one word.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7410,19 +7410,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A word-puzzle app checks whether two phrases are anagrams of each other, ignoring case and spaces.
-Read two lines of text. Convert both to lower case and remove all spaces from each. If the sorted letters of the first line match the sorted letters of the second line exactly, print `Yes`; otherwise print `No`.
+          <t>A word puzzle game checks whether a player's submitted word is an anagram of the target word — made of exactly the same letters rearranged — ignoring letter case and any spaces.
+Write a program that reads two words on separate lines, ignores case and spaces in both, and prints `Yes` if they are anagrams of each other, and `No` otherwise.
 ### Input Format
-- Line 1: First
-- Line 2: Second
+- Line 1: First word
+- Line 2: Second word
 ### Output Format
 ```
 Yes
 ```
 ### Example Walkthrough
-In the sample, the first line is `listen` and the second is `silent`. Neither has spaces, and after converting to lower case and sorting their letters, both become `eilnst`, so the program prints `Yes`.
+In the sample, the words are `listen` and `silent`. Both contain exactly the same letters, just rearranged, so the program prints `Yes`.
 ### Constraints
-- Comparison ignores letter case and spaces but considers every other character, including punctuation and digits.
+- The inputs are valid lines of text.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>

--- a/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 5 - Strings/Unit 5 - Strings - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,17 +598,11 @@
         <is>
           <t>Priya writes for her college fest's blog. Every post needs a web address, and the website builds it from the post's title: all letters made small, and every space replaced with a hyphen. This hyphen-joined, lower-case form is called a "slug" — the friendly text you see at the end of a web link.
 Write a program that reads a title on one line, converts it to lower case, replaces each space with a hyphen (`-`), and prints the resulting slug.
-### Input Format
-- Line 1: A title (words separated by spaces)
-### Output Format
-```
-hello-world
-```
 ### Example Walkthrough
 The sample input is `Hello World`. Making all letters small gives `hello world`, and replacing the space with a hyphen gives `hello-world`, which is exactly what the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -744,7 +735,7 @@
       <c r="AG2" t="inlineStr">
         <is>
           <t>title = input()
-print(title.replace(" ", "-").lower())</t>
+print(title.replace(" ", "-").lower())  # swap spaces for hyphens, then lowercase for a slug</t>
         </is>
       </c>
     </row>
@@ -758,17 +749,11 @@
         <is>
           <t>At Arjun's coaching class, the teacher plays a quick vocabulary game: she calls out a word, and students must shout back its first and last letters. Arjun wants a small program that gives the correct answer instantly.
 Read one word and print its first character and its last character, separated by a single space. If the word has only one letter, that same letter is both the first and the last, so print it twice.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-p n
-```
 ### Example Walkthrough
 The sample word is `python`. Its first character is `p` and its last character is `n`, so the program prints `p n` with one space between them.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -901,7 +886,7 @@
       <c r="AG3" t="inlineStr">
         <is>
           <t>word = input()
-print(word[0], word[-1])</t>
+print(word[0], word[-1])  # index 0 is the first char, -1 is the last char</t>
         </is>
       </c>
     </row>
@@ -915,17 +900,11 @@
         <is>
           <t>Students filling the online hostel registration form often press the spacebar by mistake before or after typing their name. The college office software must clean up these stray spaces before saving each entry, without disturbing the text in the middle.
 Read one line of text, remove any spaces at the start and end (spaces between words stay as they are), and print the cleaned text inside square brackets, like `[text]`, so the trimmed edges are easy to see.
-### Input Format
-- Line 1: A line of text that may have extra spaces at the start and end
-### Output Format
-```
-[hello]
-```
 ### Example Walkthrough
 The sample input is `  hello  ` — the word `hello` with two spaces on each side. Stripping the spaces from both ends leaves just `hello`, and wrapping it in square brackets prints `[hello]`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1059,7 +1038,7 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>text = input()
-print("[" + text.strip() + "]")</t>
+print("[" + text.strip() + "]")  # strip() removes only leading/trailing spaces</t>
         </is>
       </c>
     </row>
@@ -1073,17 +1052,11 @@
         <is>
           <t>The college library prints ID badges for its student volunteers, but long names never fit on the small card. So the badge machine prints only the person's initials — the first letter of each part of the name, in capitals.
 Read a full name (words separated by spaces), take the first letter of each word, convert those letters to capitals, and print them joined together with nothing in between.
-### Input Format
-- Line 1: A full name (words separated by spaces)
-### Output Format
-```
-JRT
-```
 ### Example Walkthrough
 The sample name `john ronald tolkien` has three words. Their first letters are `j`, `r` and `t`; capitalised and joined together they become `JRT`, which is what the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1217,8 +1190,8 @@
         <is>
           <t>name = input()
 initials = ""
-for word in name.split():
-    initials += word[0].upper()
+for word in name.split():          # split() breaks the name into separate words
+    initials += word[0].upper()    # take first letter of each word, capitalized
 print(initials)</t>
         </is>
       </c>
@@ -1233,17 +1206,11 @@
         <is>
           <t>On the long bus ride back to the hostel, Kavya and her friends play a word game: spot words that read the same forwards and backwards, like `madam`. Such a word is called a palindrome, and Kavya wants a program to settle their arguments.
 Read one word and print `Yes` if it reads the same forwards and backwards, treating capital and small letters as equal; otherwise print `No`.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-Yes
-```
 ### Example Walkthrough
 The sample word is `racecar`. Written backwards it is still `racecar`, so it is a palindrome and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1376,8 +1343,8 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>word = input().lower()
-print("Yes" if word == word[::-1] else "No")</t>
+          <t>word = input().lower()   # ignore case so Madam and madam match
+print("Yes" if word == word[::-1] else "No")   # compare word to its reverse</t>
         </is>
       </c>
     </row>
@@ -1391,18 +1358,11 @@
         <is>
           <t>The coding club's group chat has a small moderation bot. Whenever someone types a word from the banned list, the bot must hide it by replacing it with `***` before the message appears on screen.
 Read a line of text, then read the banned word on the next line. Replace every occurrence of the banned word in the text with `***` and print the resulting line.
-### Input Format
-- Line 1: A line of text
-- Line 2: The banned word
-### Output Format
-```
-this is ***
-```
 ### Example Walkthrough
 The sample text is `this is bad` and the banned word is `bad`. The word appears once, at the end, so it is replaced with `***` and the program prints `this is ***`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1543,7 +1503,7 @@
         <is>
           <t>text = input()
 word = input()
-print(text.replace(word, "***"))</t>
+print(text.replace(word, "***"))   # replace every occurrence of the banned word</t>
         </is>
       </c>
     </row>
@@ -1557,19 +1517,11 @@
         <is>
           <t>The canteen near the exam hall has installed a new billing machine. For every item sold, the machine prints one receipt line showing the item's name, how many were bought, and the total amount for that item.
 Read an item name, then a quantity (a whole number), then a unit price. Multiply the quantity by the unit price and print a line in the exact form `name x quantity = total`, with the total shown to exactly 2 decimal places.
-### Input Format
-- Line 1: Item name
-- Line 2: Quantity (a whole number)
-- Line 3: Unit price
-### Output Format
-```
-Coffee x 3 = 7.50
-```
 ### Example Walkthrough
 The sample input is `Coffee`, quantity 3 and unit price 2.5. Multiplying 3 by 2.5 gives 7.5, which written with two decimal places is `7.50`, so the program prints `Coffee x 3 = 7.50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1718,7 +1670,7 @@
           <t>item = input()
 qty = int(input())
 price = float(input())
-print(f"{item} x {qty} = {qty * price:.2f}")</t>
+print(f"{item} x {qty} = {qty * price:.2f}")   # :.2f keeps two decimal places for money</t>
         </is>
       </c>
     </row>
@@ -1732,17 +1684,11 @@
         <is>
           <t>Rohit is paying his semester exam fee online. On the payment page, his saved card number is never shown in full — for safety, every digit except the last four is hidden behind an asterisk (`*`).
 Read a card number (digits only) and print the masked version: one `*` for each digit except the last four, followed by the last four digits exactly as they are.
-### Input Format
-- Line 1: A card number (digits only)
-### Output Format
-```
-************5678
-```
 ### Example Walkthrough
 The sample number `1234567812345678` has 16 digits. The first 12 digits are each replaced by `*`, and the last four digits `5678` are kept, so the program prints `************5678`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1875,7 +1821,7 @@
       <c r="AG9" t="inlineStr">
         <is>
           <t>card = input()
-print("*" * (len(card) - 4) + card[-4:])</t>
+print("*" * (len(card) - 4) + card[-4:])   # mask all but the last four digits</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1835,11 @@
         <is>
           <t>An airline's booking system generates a short destination code for every ticket by taking just the first three letters of the city name typed in by the check-in agent.
 Write a program that reads a city name and prints only its first three characters. If the name has fewer than three characters, print the whole name.
-### Input Format
-- Line 1: City name
-### Output Format
-```
-Pyt
-```
 ### Example Walkthrough
 In the sample, the city name is `Python`. Taking the first three characters gives `Pyt`, which the program prints.
 ### Constraints
 - The input is a valid line of text with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2032,7 +1972,7 @@
       <c r="AG10" t="inlineStr">
         <is>
           <t>s=input()
-print(s[:3])</t>
+print(s[:3])   # slicing beyond the string length is safe, no error</t>
         </is>
       </c>
     </row>
@@ -2046,17 +1986,11 @@
         <is>
           <t>A grammar checker flags whether a sentence a student submits ends with proper punctuation, specifically a full stop.
 Write a program that reads a line of text and prints `Yes` if it ends with a period (`.`), and `No` otherwise.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-Yes
-```
 ### Example Walkthrough
 In the sample, the text is `Hello.`. Since the last character is a period, the program prints `Yes`. The text `Hello` (no period) would print `No`.
 ### Constraints
 - The input is a valid line of text with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2189,3088 +2123,2613 @@
       <c r="AG11" t="inlineStr">
         <is>
           <t>s=input()
-print("Yes" if s.endswith(".") else "No")</t>
+print("Yes" if s.endswith(".") else "No")   # endswith checks the final character(s)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Caesar Cipher</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Dev and Sam, two hostel roommates, pass secret notes using an old trick called the Caesar cipher: every letter in the message is shifted forward in the alphabet by a fixed number of places, wrapping around from `z` back to `a`.
 Read a lower-case message, then a number `K`. Shift each letter forward by `K` places in the alphabet (wrapping from `z` back to `a`); anything that is not a letter, like a space or a digit, stays unchanged. Print the encrypted message.
-### Input Format
-- Line 1: The message (lower-case)
-- Line 2: K, the number of places to shift
-### Output Format
-```
-bcd
-```
 ### Example Walkthrough
 The sample message is `abc` with `K = 1`. Shifting each letter forward one place turns `a` into `b`, `b` into `c`, and `c` into `d`, so the program prints `bcd`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>abc
 1</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>bcd</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>xyz
 3</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>hello
 5</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>mjqqt</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>a
 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>hello world
 1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>ifmmp xpsme</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>abc xyz
 26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>abc xyz</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>z
 25</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>text = input()
 k = int(input())
 result = ""
 for ch in text:
     if ch.isalpha():
-        result += chr((ord(ch) - 97 + k) % 26 + 97)
+        result += chr((ord(ch) - 97 + k) % 26 + 97)   # shift within a-z, wrap using %26
     else:
-        result += ch
+        result += ch     # leave non-letters unchanged
 print(result)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Anagram Check</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Ananya loves the word puzzle in the Sunday newspaper: it gives two words and asks whether one is just the other with its letters rearranged — for example `heart` and `earth`. Such a pair is called an anagram, and she wants a program to check her answers.
 Read two lines of text and print `Yes` if they are anagrams of each other — made of exactly the same letters in any order — treating capital and small letters as equal and ignoring spaces. Otherwise print `No`.
-### Input Format
-- Line 1: First text
-- Line 2: Second text
-### Output Format
-```
-Yes
-```
 ### Example Walkthrough
 The sample inputs are `listen` and `silent`. Both words use the letters `e`, `i`, `l`, `n`, `s` and `t` exactly once each, so they are anagrams and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>listen
 silent</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>hello
 world</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Dormitory
 Dirty Room</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>abc
 cba</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>aabbcc
 abcabc</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>The Morse Code
 Here Come Dots</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>a = input().lower().replace(" ", "")
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>a = input().lower().replace(" ", "")   # normalize case and drop spaces
 b = input().lower().replace(" ", "")
-print("Yes" if sorted(a) == sorted(b) else "No")</t>
+print("Yes" if sorted(a) == sorted(b) else "No")   # anagrams have identical sorted letters</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Shout It Out</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A chat app has a 'caps' button. Read one line of text and print it entirely in upper case.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-HELLO WORLD
-```
 ### Example Walkthrough
 In the sample, the input is `hello world`. Converting every letter to upper case gives `HELLO WORLD`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>HELLO WORLD</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>PYTHON</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>ALREADY UPPER</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>ALREADY UPPER</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>MiXeD CaSe 123</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>MIXED CASE 123</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>the quick brown fox jumps</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>THE QUICK BROWN FOX JUMPS</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>text = input()
-print(text.upper())</t>
+print(text.upper())   # upper() converts every letter to uppercase</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Message Length</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A text box shows a character counter. Read one line and print how many characters it contains.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, the input is `Hello`. It has `5` characters, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>string-basics</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t xml:space="preserve">   </t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>supercalifragilisticexpialidocious</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>text = input()
-print(len(text))</t>
+print(len(text))   # len() counts all characters, including spaces</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Preview Snippet</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>A search result shows only the first 3 characters of a title as a preview. Read a title and print its first 3 characters (or the whole title if it is shorter).
-### Input Format
-- Line 1: A title
-### Output Format
-```
-int
-```
 ### Example Walkthrough
 In the sample, the title is `international`. Its first three characters are `int`, so the program prints `int`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>indexing-and-slicing</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>introduction</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>hi</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>hi</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>byte</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>byt</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>This Is A Long Title</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>Thi</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>title = input()
-print(title[:3])</t>
+print(title[:3])   # slicing beyond the length just returns the whole string</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Word Count</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>A writing tool counts words. Read a line of text and print how many words it contains (words are separated by spaces).
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-4
-```
 ### Example Walkthrough
 In the sample, the input is `the quick brown fox`. It splits into `4` words, so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>the quick brown fox</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>a b c d</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t xml:space="preserve">   </t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>a  b   c    d     e</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>text = input()
-print(len(text.split()))</t>
+print(len(text.split()))   # split() on spaces gives a list of words</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Proper Name</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>A form tidies a name so each word starts with a capital letter. Read a name and print it in title case.
-### Input Format
-- Line 1: A name
-### Output Format
-```
-John Doe
-```
 ### Example Walkthrough
 In the sample, the input is `john doe`. Converting it to title case gives `John Doe`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>john doe</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>John Doe</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>mary jane watson</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Mary Jane Watson</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>alice</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>MARY JANE</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Mary Jane</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>mcdonald o'brien</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Mcdonald O'Brien</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>anne marie de la cruz</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Anne Marie De La Cruz</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>name = input()
-print(name.title())</t>
+print(name.title())   # title() capitalizes the first letter of each word</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Echo Chamber</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>A sound effect repeats a short sound N times. Read the text, then N, and print the text repeated N times with no spaces between copies.
-### Input Format
-- Line 1: The text
-- Line 2: N, the number of repeats
-### Output Format
-```
-ababab
-```
 ### Example Walkthrough
 In the sample, the text is `ab` and `N` is `3`. Repeating `ab` three times with no separator gives `ababab`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>string-basics</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>ab
 3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>ababab</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>x
 5</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>xxxxx</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>hi
 1</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>hi</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>a
 0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>hello
 2</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>hellohello</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>z
 10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>zzzzzzzzzz</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>ab
 100</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>abababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababababab</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>text = input()
 n = int(input())
-print(text * n)</t>
+print(text * n)   # string * n repeats it n times with no separator</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Clean Username</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A signup form normalizes every username before storing it in the database, so `  Asha  ` and `asha` are treated as the same account: stray spaces at the ends are trimmed and every letter is converted to lower case.
 Write a program that reads a username, removes any leading or trailing spaces, converts it to lower case, and prints the result.
-### Input Format
-- Line 1: Username
-### Output Format
-```
-asha
-```
 ### Example Walkthrough
 In the sample, the input is `  Asha  `. Trimming the spaces gives `Asha`, and converting to lower case gives `asha`, which the program prints.
 ### Constraints
 - The input is a valid line of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Asha  </t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>asha</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>ROHAN</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>rohan</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t xml:space="preserve"> Meena</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>meena</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t xml:space="preserve">Kabir </t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>kabir</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Z oya</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>z oya</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t xml:space="preserve"> DEV PATEL </t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>dev patel</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>print(input().strip().lower())</t>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>print(input().strip().lower())   # trim spaces first, then lowercase for comparison</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Join Words</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A photo-sharing app turns a caption typed with spaces into a single hashtag by joining the words together with hyphens instead of spaces.
 Write a program that reads a line of words separated by spaces and prints them joined together with a single hyphen (`-`) between each pair of words.
-### Input Format
-- Line 1: Words separated by spaces
-### Output Format
-```
-hello-world
-```
 ### Example Walkthrough
 In the sample, the input is `hello world`. Splitting it gives the words `hello` and `world`, and joining them with a hyphen gives `hello-world`, which the program prints.
 ### Constraints
 - The input is a valid line of text with at least one word.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>hello-world</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>python foundations</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>python-foundations</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>a-b-c</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Byte XL Course</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Byte-XL-Course</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>data types</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>data-types</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>clean code now</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>clean-code-now</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>print("-".join(input().split()))</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>print("-".join(input().split()))   # split on spaces, rejoin with hyphens</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Word Reverser</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a sentence and print its words in reverse order, separated by single spaces.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-world hello
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aditya is building a simple word-puzzle app where every clue is shown with its words in reverse order, so players have to unscramble the sentence to guess the answer. The app takes whatever sentence the puzzle setter types and instantly generates the reversed-order clue.
+Read a sentence and print its words in reverse order, separated by single spaces.
 ### Example Walkthrough
 In the sample, the input is `hello world`. Reversing the order of its words gives `world hello`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>world hello</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>one two three</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>three two one</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>b a</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>the quick brown fox jumps over</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>over jumps fox brown quick the</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t xml:space="preserve">  extra   spaces   here  </t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>here spaces extra</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>words = input().split()
-print(" ".join(words[::-1]))</t>
+print(" ".join(words[::-1]))   # reverse the list of words, then join with spaces</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Swap Case</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>A novelty keyboard swaps the case of every letter. Read a line and print it with upper-case letters made lower-case and vice versa.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-hELLO wORLD
-```
 ### Example Walkthrough
 In the sample, the input is `Hello World`. Swapping each letter's case gives `hELLO wORLD`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>Hello World</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>hELLO wORLD</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>PyThOn</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>pYtHoN</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>abcXYZ</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>ABCxyz</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t xml:space="preserve">
 </t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>ALLCAPS</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>allcaps</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>1234 mixed CASE 5678</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>1234 MIXED case 5678</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>text = input()
-print(text.swapcase())</t>
+print(text.swapcase())   # swapcase() flips upper to lower and lower to upper</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Find the Word</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a line of text, then a word to search for. Print the index where the word first appears, or -1 if it does not appear.
-### Input Format
-- Line 1: A line of text
-- Line 2: The word to find
-### Output Format
-```
-6
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Meera is adding a simple "find in text" feature to her note-taking app, similar to pressing Ctrl+F, that tells the user exactly where a searched word begins inside a line.
+Read a line of text, then a word to search for. Print the index where the word first appears, or -1 if it does not appear.
 ### Example Walkthrough
 In the sample, the text is `hello world` and the word to find is `world`. It first appears at index `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>hello world
 world</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>abcabc
 bc</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>python
 xyz</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t xml:space="preserve">hello
 </t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>aaaa
 aa</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>the quick brown fox
 brown</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>text = input()
 word = input()
-print(text.find(word))</t>
+print(text.find(word))   # find() returns the starting index, or -1 if missing</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Count Substring</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line of text, then a smaller piece of text. Print how many times the piece appears in the line (non-overlapping).
-### Input Format
-- Line 1: A line of text
-- Line 2: The piece to count
-### Output Format
-```
-3
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul is scanning server log lines for a particular keyword to see how often it shows up in a single line, without counting overlapping matches, so he can flag lines with repeated warnings.
+Read a line of text, then a smaller piece of text. Print how many times the piece appears in the line (non-overlapping).
 ### Example Walkthrough
 In the sample, the text is `ababab` and the piece is `ab`. It appears `3` times without overlapping, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>banana
 a</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>aaaa
 aa</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>hello
 z</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>mississippi
 ss</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>aaaaaa
 aaa</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t xml:space="preserve">hello world
  </t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>text = input()
 piece = input()
-print(text.count(piece))</t>
+print(text.count(piece))   # count() counts non-overlapping occurrences</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Email Domain</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read an email address and print just the domain part that comes after the '@' sign.
-### Input Format
-- Line 1: An email address
-### Output Format
-```
-example.com
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The IT helpdesk at a company wants to automatically sort incoming support tickets by the sender's email domain, so requests from partner organisations can be routed differently. Given someone's email address, the system first needs to pull out just the domain.
+Read an email address and print just the domain part that comes after the '@' sign.
 ### Example Walkthrough
 In the sample, the email is `user@example.com`. Splitting on `@` and keeping the second part gives `example.com`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>john@example.com</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>example.com</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>a.b@mail.co.in</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>mail.co.in</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>user@site.org</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>site.org</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>x@y.co</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>y.co</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>first.last@sub.domain.com</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>sub.domain.com</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>a1@test123.net</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>test123.net</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>name@company.io</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>company.io</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>email = input()
-print(email.split("@")[1])</t>
+print(email.split("@")[1])   # split on @ gives [name, domain], take the domain</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Starts With</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of text, then a prefix. Print 'Yes' if the text starts with that prefix, otherwise print 'No'.
-### Input Format
-- Line 1: A line of text
-- Line 2: The prefix
-### Output Format
-```
-Yes
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fatima is building a search bar for her library app. As a quick shortcut before doing a full search, she wants to check whether a book title begins with whatever text the user has typed so far.
+Read a line of text, then a prefix. Print 'Yes' if the text starts with that prefix, otherwise print 'No'.
 ### Example Walkthrough
-In the sample, the text is `hello world` and the prefix is `hello`. Since the text starts with that prefix, the program prints `Yes`.
+In the sample, the text is `python` and the prefix is `py`. Since the text starts with that prefix, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>python
 py</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>hello
 hi</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>coding
 cod</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t xml:space="preserve">hello
 </t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>abc
 abcd</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>the quick fox
 the quick</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>text = input()
 prefix = input()
-print("Yes" if text.startswith(prefix) else "No")</t>
+print("Yes" if text.startswith(prefix) else "No")   # startswith checks the beginning only</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Vowels and Consonants</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Read a line of text and print two numbers: how many vowels and how many consonants it contains, separated by a space. Count letters only and ignore case.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-5 4
-```
 ### Example Walkthrough
 In the sample, the input is `education`. It has `5` vowels (`e`, `u`, `a`, `i`, `o`) and `4` consonants (`d`, `c`, `t`, `n`), so the program prints `5 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>5 4</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>0 3</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>AEIOU bcd</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>5 3</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>1 0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>bcdfg</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>0 5</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>The Quick Brown Fox</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>5 11</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>aaaaaeeeee</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>10 0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>text = input().lower()
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>text = input().lower()   # ignore case while counting
 vowels = consonants = 0
 for ch in text:
-    if ch.isalpha():
+    if ch.isalpha():        # skip spaces, digits, punctuation
         if ch in "aeiou":
             vowels += 1
         else:
@@ -5279,1462 +4738,1228 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Middle Slice</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A text editor's "trim edges" feature strips away the very first and last character of any word a user selects, leaving just the middle portion behind.
 Write a program that reads a word and prints it with its first and last characters removed. If the word has one or two characters, print an empty line.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-ytho
-```
 ### Example Walkthrough
 In the sample, the word is `Python`. Removing the first character (`P`) and the last character (`n`) leaves `ytho`, which the program prints.
 ### Constraints
 - The input is a valid word with no spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>indexing-and-slicing</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>ytho</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>estin</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>2345</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>ByteXL</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>yteX</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>s=input()
-print(s[1:-1])</t>
+print(s[1:-1])   # slice drops the first and last character</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Count Word</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>An analytics tool checks how many times a specific keyword appears among the words of a sentence a user has typed, to measure keyword repetition. The match must be an exact, case-sensitive whole word, not a substring.
 Write a program that reads a sentence on one line and a target word on the next line, then prints how many of the sentence's space-separated words exactly match the target word.
-### Input Format
-- Line 1: A sentence (words separated by spaces)
-- Line 2: The target word
-### Output Format
-```
-2
-```
 ### Example Walkthrough
 In the sample, the sentence is `cat dog cat` and the target word is `cat`. Splitting the sentence into words gives `cat`, `dog`, and `cat`, of which two exactly match `cat`, so the program prints `2`.
 ### Constraints
 - The inputs are valid lines of text with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>cat dog cat
 cat</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>one two one
 one</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>hello
 hello</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>a a a
 a</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>red blue red
 blue</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>Python python
 Python</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>x y z
 a</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>s=input(); w=input(); print(s.split().count(w))</t>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>s=input(); w=input(); print(s.split().count(w))   # split into words, count exact matches</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Mask Email Name</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A public leaderboard shows partial email addresses for privacy: the part before the `@` is replaced with the same number of asterisks, while the domain after the `@` stays visible.
 Write a program that reads an email address and prints it with the part before the `@` replaced by that many asterisks, keeping the `@` and everything after it unchanged.
-### Input Format
-- Line 1: An email address in the form `name@domain`
-### Output Format
-```
-****@mail.com
-```
 ### Example Walkthrough
 In the sample, the email is `asha@mail.com`. The part before `@` is `asha`, which has 4 characters, so it becomes `****`, and the program prints `****@mail.com`.
 ### Constraints
 - The input is a valid email address containing exactly one `@`.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>string-methods</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>asha@mail.com</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>****@mail.com</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>r@x.in</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>*@x.in</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>meena@college.edu</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>*****@college.edu</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>dev.patel@test.org</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>*********@test.org</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>a@b.c</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>*@b.c</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>longname@site.com</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>********@site.com</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>zoya@byte.in</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>****@byte.in</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>e=input(); name,domain=e.split("@"); print("*"*len(name)+"@"+domain)</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>e=input(); name,domain=e.split("@"); print("*"*len(name)+"@"+domain)   # mask the name part, keep the domain</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Most Frequent Character</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a line of text and print the character that appears most often. If several characters tie, print the one that appears earliest in the text.
-### Input Format
-- Line 1: A line of text (no spaces)
-### Output Format
-```
-i
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Karan is exploring basic cryptography and wants a tool that scans a message to find its single most frequent character, a first step toward cracking simple substitution ciphers. When counts tie, the earliest-appearing character should win, so the result stays predictable.
+Read a line of text and print the character that appears most often. If several characters tie, print the one that appears earliest in the text.
 ### Example Walkthrough
 In the sample, the input is `mississippi`. The letters `i` and `s` both appear `4` times, but `i` appears earlier in the text, so the program prints `i`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>aabbbcc</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>abcabc</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>zzzzzzz</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>abcdefgghh</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>text = input()
 best = ""
 best_count = 0
 for ch in text:
-    count = text.count(ch)
-    if count &gt; best_count:
+    count = text.count(ch)         # how many times this character appears overall
+    if count &gt; best_count:         # strictly greater keeps the earliest tie
         best_count = count
         best = ch
 print(best)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Word Frequency</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Read a sentence and, for each distinct word in order of first appearance, print the word and how many times it appears, separated by a space, one per line.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-a 3
-b 2
-c 1
-```
 ### Example Walkthrough
 In the sample, the input is `a b a c a b`. In order of first appearance, `a` appears `3` times, `b` appears `2` times, and `c` appears `1` time, so the program prints `a 3`, `b 2`, and `c 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>a b a c b a</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>a 3
 b 2
 c 1</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>hello hello</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>hello 2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>one two two three three three</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>one 1
 two 2
 three 3</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>a 1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>x 1
 y 1
 z 1</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>same same same same</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>same 4</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>a b c a b c a b c a</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>a 4
 b 3
 c 3</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>words = input().split()
 seen = []
 for w in words:
-    if w not in seen:
+    if w not in seen:      # record each distinct word once, in first-seen order
         seen.append(w)
 for w in seen:
-    print(w, words.count(w))</t>
+    print(w, words.count(w))   # count() gives total occurrences of that word</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Make an Acronym</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a phrase and print its acronym: the capitalised first letter of each word, joined together.
-### Input Format
-- Line 1: A phrase
-### Output Format
-```
-RAM
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Priyanka takes minutes for her office's recurring project meetings and likes to give each one a short acronym so it is easy to reference in emails and calendar invites.
+Read a phrase and print its acronym: the capitalised first letter of each word, joined together.
 ### Example Walkthrough
 In the sample, the phrase is `random access memory`. Taking the capitalised first letter of each word gives `R`, `A`, and `M`, joined into `RAM`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>random access memory</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>RAM</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>portable document format</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>as soon as possible</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>ASAP</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>already Capitalized Words</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>ACW</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>a b c d e f g h</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>ABCDEFGH</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>words = input().split()
 acronym = ""
 for w in words:
-    acronym += w[0].upper()
+    acronym += w[0].upper()   # take first letter of each word, uppercase
 print(acronym)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Remove Duplicate Characters</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a word and print it with duplicate characters removed, keeping only the first occurrence of each character in order.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-progamin
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Devika is designing a simple word game where a "cleaned" version of each word is shown with repeated letters stripped away, keeping only each letter's first appearance, to test how well players can still recognise the word.
+Read a word and print it with duplicate characters removed, keeping only the first occurrence of each character in order.
 ### Example Walkthrough
 In the sample, the word is `programming`. Keeping only the first occurrence of each character in order gives `progamin`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>searching-and-membership</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>programming</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>progamin</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>aabbcc</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>abcabc</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>aaaaaaa</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>abcdef</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>misp</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>word = input()
 result = ""
 for ch in word:
-    if ch not in result:
+    if ch not in result:   # only add a character the first time it's seen
         result += ch
 print(result)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Run-Length Encoding</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Compress a word by replacing runs of the same character with the character followed by how many times it repeats. For example 'aaabbc' becomes 'a3b2c1'. Read a word and print its compressed form.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-a3b2c1
-```
 ### Example Walkthrough
 In the sample, the word is `aaabbc`. The runs are three `a`s, two `b`s, and one `c`, so the program prints `a3b2c1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>indexing-and-slicing</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>aaabbc</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>a3b2c1</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>a1b1c1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>wwwwww</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>w6</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>a1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>aabbccddee</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>a2b2c2d2e2</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>z1</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>aaaaaaaaaabbbbbbbbbb</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>a10b10</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>word = input()
 result = ""
@@ -6742,280 +5967,267 @@
 while i &lt; len(word):
     ch = word[i]
     count = 1
-    while i + count &lt; len(word) and word[i + count] == ch:
+    while i + count &lt; len(word) and word[i + count] == ch:   # extend while the run continues
         count += 1
-    result += ch + str(count)
-    i += count
+    result += ch + str(count)   # record the character and its run length
+    i += count                  # jump past the whole run
 print(result)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Longest Word</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a sentence and print its longest word. If several words tie for the longest, print the one that appears first.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-quick
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A vocabulary-building app highlights the longest word in a sentence for students to look up, since longer words are more likely to be unfamiliar. When two words tie for the longest, the app highlights whichever one appears first.
+Read a sentence and print its longest word. If several words tie for the longest, print the one that appears first.
 ### Example Walkthrough
 In the sample, the input is `the quick brown fox`. `quick` and `brown` are tied for longest at `5` letters, but `quick` appears first, so the program prints `quick`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>the quick brown fox</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>i love programming</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>programming</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>a bb ccc dd</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>ccc</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>same size word test</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>a bb aa cc</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>bb</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>supercalifragilistic is long but hi is not</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>supercalifragilistic</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>words = input().split()
-best = words[0]
+best = words[0]   # start with the first word as the current longest
 for w in words[1:]:
-    if len(w) &gt; len(best):
+    if len(w) &gt; len(best):   # strictly greater keeps the earliest tie
         best = w
 print(best)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Last Name First</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>A directory lists people as 'Last, First'. Read `N`, then `N` lines each with a first and last name separated by a space, and print each name reformatted as 'Last, First', one per line.
-### Input Format
-- Line 1: N
-- Next N lines: 'first last'
-### Output Format
-```
-doe, john
-jane, mary
-```
 ### Example Walkthrough
 In the sample, `N` is `2` with `john doe` and `mary jane`. Reformatting each gives `doe, john` and `jane, mary`, printed one per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>string-formatting</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>2
 john doe
 mary jane</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>doe, john
 jane, mary</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>1
 alice smith</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>smith, alice</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>3
 a b
@@ -7023,30 +6235,30 @@
 e f</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>b, a
 d, c
 f, e</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>1
 x y</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>y, x</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>4
 a b
@@ -7055,7 +6267,7 @@
 g h</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>b, a
 d, c
@@ -7063,506 +6275,489 @@
 h, g</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>2
 john ronald
 mary jane</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>ronald, john
 jane, mary</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>n = int(input())
 for _ in range(n):
-    first, last = input().split()
+    first, last = input().split()   # unpack the line into two names
     print(f"{last}, {first}")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Compress Runs</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A simple image tool draws pixel rows as sequences of colored strokes, and compresses each row for storage by writing each repeated color once followed by how many pixels in a row had that color.
 Write a program that reads a string and prints its run-length encoding: each maximal run of the same consecutive character replaced by that character followed by the count of how many times it repeats, with no separators between runs.
-### Input Format
-- Line 1: A string with no spaces
-### Output Format
-```
-a3b2
-```
 ### Example Walkthrough
 In the sample, the string is `aaabb`. The first run is `a` repeated 3 times (`a3`), followed by `b` repeated 2 times (`b2`), so the program prints `a3b2`.
 ### Constraints
 - The input is a valid non-empty string with no spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>text-processing</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>aaabb</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>a3b2</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>a1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>a1b1c1</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>zzzz</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>z4</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>aabcccccaaa</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>a2b1c5a3</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>111223</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>132231</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>s=input(); out=[]; prev=s[0]; c=1
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>s=input(); out=[]; prev=s[0]; c=1   # prev tracks the current run's character, c its length
 for ch in s[1:]:
  if ch==prev: c+=1
- else: out.append(prev+str(c)); prev=ch; c=1
-out.append(prev+str(c))
+ else: out.append(prev+str(c)); prev=ch; c=1   # run ended, save it and start a new one
+out.append(prev+str(c))   # save the final run after the loop
 print("".join(out))</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Reverse Words</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A teleprompter app has a "word-order drill" mode for practicing sentences backwards: it takes a sentence and reads the words out in reverse order, without spelling any individual word backwards.
 Write a program that reads a sentence and prints its words in reverse order, separated by single spaces.
-### Input Format
-- Line 1: A sentence (words separated by spaces)
-### Output Format
-```
-three two one
-```
 ### Example Walkthrough
 In the sample, the sentence is `one two three`. Splitting it into words gives `one`, `two`, `three`, and reversing their order gives `three`, `two`, `one`, so the program prints `three two one`.
 ### Constraints
 - The input is a valid line of text with at least one word.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>split-and-join</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>one two three</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>three two one</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>b a</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Python is fun</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>fun is Python</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>spaced words</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>words spaced</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>x y z q</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>q z y x</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>ByteXL course</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>course ByteXL</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>print(" ".join(input().split()[::-1]))</t>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>print(" ".join(input().split()[::-1]))   # split into words, reverse order, rejoin with spaces</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Anagram Sorted</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A word puzzle game checks whether a player's submitted word is an anagram of the target word — made of exactly the same letters rearranged — ignoring letter case and any spaces.
 Write a program that reads two words on separate lines, ignores case and spaces in both, and prints `Yes` if they are anagrams of each other, and `No` otherwise.
-### Input Format
-- Line 1: First word
-- Line 2: Second word
-### Output Format
-```
-Yes
-```
 ### Example Walkthrough
 In the sample, the words are `listen` and `silent`. Both contain exactly the same letters, just rearranged, so the program prints `Yes`.
 ### Constraints
 - The inputs are valid lines of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>strings</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>text-processing</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>listen
 silent</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>abc
 abd</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>triangle
 integral</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>Dormitory
 dirtyroom</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>rat
 tar</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>hello
 world</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>a=input().lower().replace(" ",""); b=input().lower().replace(" ",""); print("Yes" if sorted(a)==sorted(b) else "No")</t>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>a=input().lower().replace(" ","")   # normalize case and drop spaces
+b=input().lower().replace(" ","")
+print("Yes" if sorted(a)==sorted(b) else "No")   # anagrams share the same sorted letters</t>
         </is>
       </c>
     </row>
